--- a/data/trans_orig/IP40-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP40-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según como llegan a fin de mes con los ingresos de su hogar en 2012 (tasa de respuesta: 97,0%)</t>
+          <t>Adultos según como llegan a fin de mes con los ingresos de su hogar en 2012 (tasa de respuesta: 97,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>694</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6539</t>
+          <t>6590</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>638</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5310</t>
+          <t>5687</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1714</t>
+          <t>1578</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9469</t>
+          <t>8891</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>6858</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17753</t>
+          <t>18002</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14547</t>
+          <t>14231</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27922</t>
+          <t>29069</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23983</t>
+          <t>23779</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41029</t>
+          <t>40876</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,42%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21552</t>
+          <t>21593</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36442</t>
+          <t>36531</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20041</t>
+          <t>19463</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35005</t>
+          <t>34656</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>43981</t>
+          <t>44103</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>67011</t>
+          <t>65529</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,12%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39570</t>
+          <t>39969</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57257</t>
+          <t>57959</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32751</t>
+          <t>32630</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50374</t>
+          <t>50728</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>77285</t>
+          <t>75647</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>101803</t>
+          <t>101412</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,78%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20856</t>
+          <t>21386</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35760</t>
+          <t>36432</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22477</t>
+          <t>21165</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>38932</t>
+          <t>37936</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>46629</t>
+          <t>46477</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>69430</t>
+          <t>68567</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,19%</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19176</t>
+          <t>18452</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34208</t>
+          <t>34397</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1312,12 +1312,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13437</t>
+          <t>13268</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26907</t>
+          <t>26827</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1367,12 +1367,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>35554</t>
+          <t>35462</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>56518</t>
+          <t>55682</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,65%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1608</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9033</t>
+          <t>8854</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1241</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8265</t>
+          <t>8055</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3890</t>
+          <t>4230</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12483</t>
+          <t>14014</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16129</t>
+          <t>16009</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30585</t>
+          <t>31359</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>26744</t>
+          <t>27397</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>45528</t>
+          <t>46354</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>46980</t>
+          <t>47166</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>70405</t>
+          <t>70940</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42847</t>
+          <t>44062</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65592</t>
+          <t>64858</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42624</t>
+          <t>41994</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63092</t>
+          <t>64449</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>91418</t>
+          <t>90184</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>122500</t>
+          <t>120010</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,48%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>57694</t>
+          <t>57371</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>80018</t>
+          <t>80009</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>65025</t>
+          <t>66557</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>90681</t>
+          <t>91078</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>131052</t>
+          <t>131171</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>164935</t>
+          <t>163133</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,28%</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>40101</t>
+          <t>39728</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>61097</t>
+          <t>59531</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>36941</t>
+          <t>36555</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>57496</t>
+          <t>57455</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>80718</t>
+          <t>80174</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>110810</t>
+          <t>111146</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,67%</t>
         </is>
       </c>
     </row>
@@ -2092,12 +2092,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25186</t>
+          <t>25586</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43084</t>
+          <t>43060</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2107,82 +2107,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>18,6%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>42573</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>32901</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>53089</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>16,46%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>12,72%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>20,52%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>76394</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>64601</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>91205</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>15,58%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>13,18%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t>18,61%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>42573</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>33189</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>53880</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>16,46%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>12,83%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>20,83%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>76394</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>63811</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>89448</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>15,58%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>13,02%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>18,25%</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4719</t>
+          <t>5201</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4587</t>
+          <t>5242</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13120</t>
+          <t>12879</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26713</t>
+          <t>27677</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11868</t>
+          <t>12300</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24949</t>
+          <t>25639</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>27502</t>
+          <t>27767</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>48371</t>
+          <t>47120</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,29%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>26222</t>
+          <t>26008</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>42772</t>
+          <t>41844</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25579</t>
+          <t>25557</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43390</t>
+          <t>41853</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>56783</t>
+          <t>56101</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>80495</t>
+          <t>80946</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,26%</t>
         </is>
       </c>
     </row>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>33849</t>
+          <t>34504</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>52042</t>
+          <t>52665</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>38121</t>
+          <t>37684</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>56664</t>
+          <t>56582</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2731,12 +2731,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>77147</t>
+          <t>75852</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>102598</t>
+          <t>102317</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2746,12 +2746,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,2%</t>
         </is>
       </c>
     </row>
@@ -2774,12 +2774,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27998</t>
+          <t>29328</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44636</t>
+          <t>45625</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2809,12 +2809,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22647</t>
+          <t>22085</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38523</t>
+          <t>38404</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>55511</t>
+          <t>55371</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>80018</t>
+          <t>80106</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,99%</t>
         </is>
       </c>
     </row>
@@ -2887,12 +2887,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14374</t>
+          <t>13812</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>28177</t>
+          <t>28222</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2922,12 +2922,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>20226</t>
+          <t>19992</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>35479</t>
+          <t>35798</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2957,12 +2957,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>38587</t>
+          <t>38051</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>59073</t>
+          <t>58029</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>18,83%</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3446</t>
+          <t>3006</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3248</t>
+          <t>2957</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13106</t>
+          <t>13302</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>27607</t>
+          <t>28281</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10904</t>
+          <t>10680</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23267</t>
+          <t>23229</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>27101</t>
+          <t>26782</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>45832</t>
+          <t>45750</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,47%</t>
         </is>
       </c>
     </row>
@@ -3343,12 +3343,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>28596</t>
+          <t>29452</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>46136</t>
+          <t>48163</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3358,12 +3358,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>36946</t>
+          <t>37842</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>56016</t>
+          <t>56080</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>70222</t>
+          <t>72183</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>96894</t>
+          <t>97965</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,85%</t>
         </is>
       </c>
     </row>
@@ -3456,12 +3456,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>51137</t>
+          <t>50159</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>72185</t>
+          <t>71286</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3471,12 +3471,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>43613</t>
+          <t>43650</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>64397</t>
+          <t>64032</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>99812</t>
+          <t>101319</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>129590</t>
+          <t>129797</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,23%</t>
         </is>
       </c>
     </row>
@@ -3569,12 +3569,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>20466</t>
+          <t>20405</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>35986</t>
+          <t>36449</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>24406</t>
+          <t>24725</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>41348</t>
+          <t>41504</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3619,12 +3619,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>49741</t>
+          <t>49261</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>73753</t>
+          <t>72767</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3654,12 +3654,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,43%</t>
         </is>
       </c>
     </row>
@@ -3682,12 +3682,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>12044</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26423</t>
+          <t>26135</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3697,12 +3697,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3717,12 +3717,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>18836</t>
+          <t>18019</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>33618</t>
+          <t>33965</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3732,12 +3732,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3752,12 +3752,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>33698</t>
+          <t>34411</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>54482</t>
+          <t>54666</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3767,12 +3767,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,1%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3474</t>
+          <t>3531</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>13111</t>
+          <t>12573</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>3031</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>12347</t>
+          <t>12402</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>8455</t>
+          <t>8551</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>21515</t>
+          <t>21366</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -4025,12 +4025,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>59868</t>
+          <t>59835</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>88874</t>
+          <t>86560</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4060,12 +4060,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>76279</t>
+          <t>76171</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>106078</t>
+          <t>104941</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4075,12 +4075,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4095,12 +4095,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>144977</t>
+          <t>143641</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>184708</t>
+          <t>185964</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4110,12 +4110,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -4138,12 +4138,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>135553</t>
+          <t>136507</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>173318</t>
+          <t>168659</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>140214</t>
+          <t>139808</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>175205</t>
+          <t>175891</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>284671</t>
+          <t>285847</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>337139</t>
+          <t>336994</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4223,12 +4223,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,71%</t>
         </is>
       </c>
     </row>
@@ -4251,12 +4251,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>200067</t>
+          <t>200493</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>239366</t>
+          <t>239882</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4266,12 +4266,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>199395</t>
+          <t>200468</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>239830</t>
+          <t>240844</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4301,12 +4301,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>412440</t>
+          <t>413216</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>470784</t>
+          <t>471302</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,16%</t>
         </is>
       </c>
     </row>
@@ -4364,12 +4364,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>124938</t>
+          <t>127095</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>160360</t>
+          <t>159388</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4379,12 +4379,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>122897</t>
+          <t>122080</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>157793</t>
+          <t>156610</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>255039</t>
+          <t>257222</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>304220</t>
+          <t>303775</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,37%</t>
         </is>
       </c>
     </row>
@@ -4477,12 +4477,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>85238</t>
+          <t>83187</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>116007</t>
+          <t>111461</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4492,12 +4492,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4512,12 +4512,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>99408</t>
+          <t>98651</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>131142</t>
+          <t>131094</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>190306</t>
+          <t>191498</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>233770</t>
+          <t>236707</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,65%</t>
         </is>
       </c>
     </row>
@@ -4744,7 +4744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según como llegan a fin de mes con los ingresos de su hogar en 2016 (tasa de respuesta: 98,82%)</t>
+          <t>Adultos según como llegan a fin de mes con los ingresos de su hogar en 2016 (tasa de respuesta: 98,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1356</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7793</t>
+          <t>8136</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4937</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2124</t>
+          <t>2214</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9799</t>
+          <t>10287</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8451</t>
+          <t>8774</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20063</t>
+          <t>18712</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9706</t>
+          <t>9460</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20815</t>
+          <t>21503</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20272</t>
+          <t>20842</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36460</t>
+          <t>36288</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -5165,12 +5165,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27047</t>
+          <t>25844</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43051</t>
+          <t>42249</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5180,12 +5180,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20999</t>
+          <t>21027</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36140</t>
+          <t>35809</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5215,12 +5215,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>52038</t>
+          <t>51644</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>73727</t>
+          <t>73603</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5250,12 +5250,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,07%</t>
         </is>
       </c>
     </row>
@@ -5278,12 +5278,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31009</t>
+          <t>30182</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47501</t>
+          <t>46467</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5293,12 +5293,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24686</t>
+          <t>25450</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40846</t>
+          <t>41747</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>60703</t>
+          <t>62013</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84217</t>
+          <t>84352</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,31%</t>
         </is>
       </c>
     </row>
@@ -5391,12 +5391,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17662</t>
+          <t>17687</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>32059</t>
+          <t>31960</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5406,12 +5406,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>20960</t>
+          <t>20936</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>36325</t>
+          <t>36039</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>43137</t>
+          <t>42630</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>64963</t>
+          <t>63039</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>24,89%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10854</t>
+          <t>10414</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23070</t>
+          <t>22223</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11496</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24457</t>
+          <t>24735</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>25463</t>
+          <t>24998</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>42955</t>
+          <t>41780</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,5%</t>
         </is>
       </c>
     </row>
@@ -5739,7 +5739,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5753</t>
+          <t>7064</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>646</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6383</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1703</t>
+          <t>1806</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8759</t>
+          <t>9236</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -5847,12 +5847,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13455</t>
+          <t>14053</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27031</t>
+          <t>26898</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5862,12 +5862,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24389</t>
+          <t>23813</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>42180</t>
+          <t>42630</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>42464</t>
+          <t>42070</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>63922</t>
+          <t>62997</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,6%</t>
         </is>
       </c>
     </row>
@@ -5960,12 +5960,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40049</t>
+          <t>40013</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60128</t>
+          <t>59593</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40988</t>
+          <t>40815</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61400</t>
+          <t>60709</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>86051</t>
+          <t>86765</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>115327</t>
+          <t>115814</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6045,12 +6045,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,01%</t>
         </is>
       </c>
     </row>
@@ -6073,12 +6073,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>49489</t>
+          <t>50048</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70133</t>
+          <t>70348</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6108,12 +6108,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>60285</t>
+          <t>61561</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>84506</t>
+          <t>84317</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>116672</t>
+          <t>118317</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>147624</t>
+          <t>150735</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>32,55%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37082</t>
+          <t>36244</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>56216</t>
+          <t>55255</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>48828</t>
+          <t>49127</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>71436</t>
+          <t>71606</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>92404</t>
+          <t>91013</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>120600</t>
+          <t>120212</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>25,96%</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22783</t>
+          <t>23081</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39512</t>
+          <t>38906</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6314,49 +6314,49 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>18,81%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>38399</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>30206</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>48939</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>14,99%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>11,79%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
           <t>19,1%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>38399</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>29757</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>48270</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>14,99%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>11,61%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>18,84%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>105</t>
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>57074</t>
+          <t>57344</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>81774</t>
+          <t>81969</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,7%</t>
         </is>
       </c>
     </row>
@@ -6529,12 +6529,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>596</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5495</t>
+          <t>5153</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6564,12 +6564,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>647</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>5811</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6579,12 +6579,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6599,12 +6599,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8544</t>
+          <t>8386</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6614,12 +6614,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -6642,12 +6642,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14520</t>
+          <t>14116</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28581</t>
+          <t>27795</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6657,12 +6657,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6677,12 +6677,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18248</t>
+          <t>18037</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34497</t>
+          <t>33882</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6712,12 +6712,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36862</t>
+          <t>36465</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>57908</t>
+          <t>57212</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,33%</t>
         </is>
       </c>
     </row>
@@ -6755,12 +6755,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>26238</t>
+          <t>26759</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>43770</t>
+          <t>43971</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6770,12 +6770,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6790,12 +6790,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29501</t>
+          <t>29528</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>47294</t>
+          <t>47638</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6825,12 +6825,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>60110</t>
+          <t>60750</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>86274</t>
+          <t>85981</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,04%</t>
         </is>
       </c>
     </row>
@@ -6868,12 +6868,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>41998</t>
+          <t>41289</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>61537</t>
+          <t>60515</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>40447</t>
+          <t>40436</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>60837</t>
+          <t>60560</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6923,7 +6923,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6938,12 +6938,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>87219</t>
+          <t>86595</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>114899</t>
+          <t>115664</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>31,0%</t>
         </is>
       </c>
     </row>
@@ -6981,12 +6981,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28615</t>
+          <t>29231</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>46280</t>
+          <t>45989</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7016,12 +7016,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30386</t>
+          <t>30969</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>50077</t>
+          <t>49648</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7051,12 +7051,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>64442</t>
+          <t>65370</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>88525</t>
+          <t>90454</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>24,24%</t>
         </is>
       </c>
     </row>
@@ -7094,12 +7094,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>32562</t>
+          <t>33803</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>51641</t>
+          <t>53000</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7109,12 +7109,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7129,12 +7129,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>22757</t>
+          <t>22744</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>39713</t>
+          <t>39648</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7164,12 +7164,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>60444</t>
+          <t>60906</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>84378</t>
+          <t>85744</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,98%</t>
         </is>
       </c>
     </row>
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>4993</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4744</t>
+          <t>4994</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -7437,12 +7437,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11882</t>
+          <t>11766</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>27023</t>
+          <t>26455</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7452,12 +7452,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7472,12 +7472,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14692</t>
+          <t>15136</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>28930</t>
+          <t>29449</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7487,12 +7487,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>30309</t>
+          <t>30102</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>50491</t>
+          <t>50423</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,65%</t>
         </is>
       </c>
     </row>
@@ -7550,12 +7550,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>28088</t>
+          <t>28442</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>45985</t>
+          <t>45758</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7565,12 +7565,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7585,12 +7585,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>24482</t>
+          <t>24452</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>40994</t>
+          <t>42217</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>56416</t>
+          <t>57517</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>80769</t>
+          <t>81808</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,77%</t>
         </is>
       </c>
     </row>
@@ -7663,12 +7663,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>39307</t>
+          <t>40372</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>60993</t>
+          <t>59496</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7678,12 +7678,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7698,12 +7698,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>35743</t>
+          <t>35253</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>55424</t>
+          <t>54661</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>81651</t>
+          <t>80474</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>110612</t>
+          <t>109320</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>31,76%</t>
         </is>
       </c>
     </row>
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>29707</t>
+          <t>30284</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>48296</t>
+          <t>48664</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7811,12 +7811,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>36186</t>
+          <t>36121</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>55285</t>
+          <t>55379</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>70990</t>
+          <t>70651</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>97743</t>
+          <t>97366</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,29%</t>
         </is>
       </c>
     </row>
@@ -7889,12 +7889,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>19647</t>
+          <t>20230</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>36302</t>
+          <t>37081</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7924,12 +7924,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>20504</t>
+          <t>20713</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>36772</t>
+          <t>37171</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7939,12 +7939,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7959,12 +7959,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>44351</t>
+          <t>45066</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>67240</t>
+          <t>68065</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7974,12 +7974,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -8119,12 +8119,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3795</t>
+          <t>3907</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>13028</t>
+          <t>13233</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8154,12 +8154,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3896</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>12421</t>
+          <t>13700</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>9654</t>
+          <t>9769</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>23540</t>
+          <t>22486</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -8232,12 +8232,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>60915</t>
+          <t>60459</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>86303</t>
+          <t>86938</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8267,12 +8267,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>80108</t>
+          <t>78152</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>109800</t>
+          <t>108435</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>147568</t>
+          <t>145951</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>187764</t>
+          <t>185976</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -8345,12 +8345,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>137824</t>
+          <t>136679</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>173347</t>
+          <t>173983</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8360,12 +8360,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8380,12 +8380,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>130992</t>
+          <t>132477</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>168051</t>
+          <t>166536</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8395,12 +8395,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8415,12 +8415,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>280353</t>
+          <t>278243</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>331754</t>
+          <t>327684</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8430,12 +8430,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>22,86%</t>
         </is>
       </c>
     </row>
@@ -8458,12 +8458,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>180292</t>
+          <t>180552</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>218531</t>
+          <t>217622</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8473,12 +8473,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>179120</t>
+          <t>181088</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>220435</t>
+          <t>221008</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8508,12 +8508,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8528,12 +8528,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>368336</t>
+          <t>369390</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>426658</t>
+          <t>426279</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8543,12 +8543,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,73%</t>
         </is>
       </c>
     </row>
@@ -8571,12 +8571,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>129042</t>
+          <t>128015</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>162580</t>
+          <t>161532</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8586,12 +8586,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>155211</t>
+          <t>156139</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>194400</t>
+          <t>193412</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8621,12 +8621,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>294078</t>
+          <t>294173</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>345331</t>
+          <t>344930</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8656,12 +8656,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -8684,12 +8684,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>100496</t>
+          <t>101180</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>130854</t>
+          <t>133191</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8699,12 +8699,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8719,12 +8719,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>97531</t>
+          <t>97817</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>131330</t>
+          <t>132377</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8734,47 +8734,47 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
+          <t>17,92%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>230757</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>207773</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>254953</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>16,1%</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>14,49%</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
           <t>17,78%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>230757</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>206734</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>253923</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>16,1%</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>14,42%</t>
-        </is>
-      </c>
-      <c r="W37" s="2" t="inlineStr">
-        <is>
-          <t>17,71%</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según como llegan a fin de mes con los ingresos de su hogar en 2023 (tasa de respuesta: 99,57%)</t>
+          <t>Adultos según como llegan a fin de mes con los ingresos de su hogar en 2023 (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9146,12 +9146,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>400</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4159</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9161,12 +9161,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9186,7 +9186,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4430</t>
+          <t>3844</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6293</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -9259,12 +9259,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6972</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16092</t>
+          <t>15569</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9274,12 +9274,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9294,12 +9294,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9143</t>
+          <t>9506</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19063</t>
+          <t>19954</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18775</t>
+          <t>18629</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31561</t>
+          <t>32002</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,22%</t>
         </is>
       </c>
     </row>
@@ -9372,12 +9372,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15480</t>
+          <t>15713</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26326</t>
+          <t>26235</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9387,12 +9387,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9407,12 +9407,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17663</t>
+          <t>17497</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29090</t>
+          <t>28960</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>35741</t>
+          <t>35505</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>51863</t>
+          <t>51538</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>43,84%</t>
         </is>
       </c>
     </row>
@@ -9485,12 +9485,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10503</t>
+          <t>10577</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20096</t>
+          <t>20894</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9500,12 +9500,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10543</t>
+          <t>10379</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20635</t>
+          <t>20275</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9535,12 +9535,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24575</t>
+          <t>23871</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38954</t>
+          <t>38141</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9570,12 +9570,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>32,44%</t>
         </is>
       </c>
     </row>
@@ -9598,12 +9598,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1718</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7870</t>
+          <t>7289</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9613,12 +9613,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9633,12 +9633,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4644</t>
+          <t>4187</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12914</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9648,12 +9648,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9668,12 +9668,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7322</t>
+          <t>7551</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17232</t>
+          <t>17429</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9683,12 +9683,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,82%</t>
         </is>
       </c>
     </row>
@@ -9711,12 +9711,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1889</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7613</t>
+          <t>8265</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9726,12 +9726,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9751,7 +9751,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2168</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8378</t>
+          <t>8205</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -9941,12 +9941,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>610</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5754</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9956,12 +9956,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2223</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9996,7 +9996,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>788</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>6054</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10031,7 +10031,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -10054,12 +10054,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30526</t>
+          <t>29262</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47891</t>
+          <t>46442</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10069,12 +10069,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24132</t>
+          <t>24351</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>41628</t>
+          <t>41776</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10104,12 +10104,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>58886</t>
+          <t>58776</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>83368</t>
+          <t>82628</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10139,12 +10139,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,74%</t>
         </is>
       </c>
     </row>
@@ -10167,12 +10167,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35080</t>
+          <t>35432</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56619</t>
+          <t>54181</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10182,12 +10182,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41339</t>
+          <t>40772</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62521</t>
+          <t>60768</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10217,12 +10217,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>82050</t>
+          <t>82817</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>109946</t>
+          <t>111035</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10252,12 +10252,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,24%</t>
         </is>
       </c>
     </row>
@@ -10280,12 +10280,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>43959</t>
+          <t>44761</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>64591</t>
+          <t>63741</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10295,12 +10295,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10315,12 +10315,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49066</t>
+          <t>48520</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70431</t>
+          <t>70599</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10330,12 +10330,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>98620</t>
+          <t>99054</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>127290</t>
+          <t>128954</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10365,12 +10365,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>38,61%</t>
         </is>
       </c>
     </row>
@@ -10393,12 +10393,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14281</t>
+          <t>14607</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10408,12 +10408,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10428,12 +10428,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18275</t>
+          <t>19113</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33675</t>
+          <t>35981</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10443,12 +10443,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10463,12 +10463,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>27091</t>
+          <t>26029</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>45427</t>
+          <t>45790</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10478,12 +10478,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -10506,12 +10506,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3902</t>
+          <t>3833</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11571</t>
+          <t>11718</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10521,82 +10521,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>7,56%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>10157</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>5711</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>16919</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>5,67%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>9,45%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>17247</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>11278</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>24904</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>5,16%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>3,38%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t>7,46%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>10157</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>5798</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>17180</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>5,67%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>9,6%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>17247</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>11505</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>24954</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>5,16%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -10736,12 +10736,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7623</t>
+          <t>8163</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10751,12 +10751,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10771,12 +10771,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>898</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8542</t>
+          <t>8614</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10786,12 +10786,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10806,12 +10806,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3316</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13526</t>
+          <t>13723</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10821,12 +10821,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -10849,12 +10849,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23683</t>
+          <t>24507</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40840</t>
+          <t>41677</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10864,12 +10864,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10884,12 +10884,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28911</t>
+          <t>30005</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49994</t>
+          <t>51277</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10899,12 +10899,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10919,12 +10919,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>58022</t>
+          <t>58124</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>84950</t>
+          <t>84167</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10934,12 +10934,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -10962,12 +10962,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41941</t>
+          <t>41962</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>62406</t>
+          <t>62488</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10977,12 +10977,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10997,12 +10997,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>77944</t>
+          <t>79101</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>106149</t>
+          <t>106852</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11012,12 +11012,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>51,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11032,12 +11032,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>127138</t>
+          <t>125774</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>160969</t>
+          <t>163444</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11047,12 +11047,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>43,38%</t>
         </is>
       </c>
     </row>
@@ -11075,12 +11075,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>40820</t>
+          <t>40272</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>60779</t>
+          <t>61309</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11090,12 +11090,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11110,12 +11110,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>35419</t>
+          <t>35634</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>59607</t>
+          <t>58767</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11125,12 +11125,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11145,12 +11145,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>81990</t>
+          <t>82766</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>115545</t>
+          <t>113024</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11160,12 +11160,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,0%</t>
         </is>
       </c>
     </row>
@@ -11188,12 +11188,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17318</t>
+          <t>16207</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40042</t>
+          <t>38392</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11203,12 +11203,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11223,12 +11223,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11527</t>
+          <t>12080</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25786</t>
+          <t>25938</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11238,12 +11238,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11258,12 +11258,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32027</t>
+          <t>32167</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>58241</t>
+          <t>58178</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11273,12 +11273,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,44%</t>
         </is>
       </c>
     </row>
@@ -11301,12 +11301,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2187</t>
+          <t>2204</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9925</t>
+          <t>9520</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11316,12 +11316,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11336,12 +11336,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>4994</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>18672</t>
+          <t>17935</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11351,12 +11351,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11371,12 +11371,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8942</t>
+          <t>9137</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>24139</t>
+          <t>24243</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11386,12 +11386,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -11531,12 +11531,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>683</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7169</t>
+          <t>7152</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11546,7 +11546,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -11601,12 +11601,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>691</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6785</t>
+          <t>6558</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11616,12 +11616,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -11644,12 +11644,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>34986</t>
+          <t>34300</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>63931</t>
+          <t>64286</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11659,12 +11659,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11679,12 +11679,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>51632</t>
+          <t>51717</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>83591</t>
+          <t>83562</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11694,12 +11694,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11714,12 +11714,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>94873</t>
+          <t>95162</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>136217</t>
+          <t>138296</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,68%</t>
         </is>
       </c>
     </row>
@@ -11757,12 +11757,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>54784</t>
+          <t>53256</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>91070</t>
+          <t>92655</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11772,12 +11772,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11792,12 +11792,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>67652</t>
+          <t>67876</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>99834</t>
+          <t>99468</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11827,12 +11827,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>126307</t>
+          <t>132594</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>180747</t>
+          <t>183503</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,74%</t>
         </is>
       </c>
     </row>
@@ -11870,12 +11870,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>52051</t>
+          <t>49059</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>89915</t>
+          <t>90192</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11885,12 +11885,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11905,12 +11905,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>95134</t>
+          <t>97780</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>140495</t>
+          <t>141933</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11940,12 +11940,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>154460</t>
+          <t>157418</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>218552</t>
+          <t>224812</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>40,11%</t>
         </is>
       </c>
     </row>
@@ -11983,12 +11983,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>23635</t>
+          <t>22624</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>114459</t>
+          <t>117891</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11998,12 +11998,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12018,12 +12018,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>16633</t>
+          <t>15734</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>34884</t>
+          <t>33487</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12053,12 +12053,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>45548</t>
+          <t>45285</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>168610</t>
+          <t>143447</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>25,59%</t>
         </is>
       </c>
     </row>
@@ -12096,12 +12096,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4903</t>
+          <t>4584</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>15979</t>
+          <t>15494</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12111,12 +12111,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12131,12 +12131,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4731</t>
+          <t>4617</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>15711</t>
+          <t>16052</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12166,12 +12166,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>11143</t>
+          <t>10626</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>26867</t>
+          <t>26278</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -12326,12 +12326,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5979</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>16366</t>
+          <t>16590</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12341,12 +12341,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12361,12 +12361,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2398</t>
+          <t>2532</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>10844</t>
+          <t>10480</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>9454</t>
+          <t>9559</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>22525</t>
+          <t>22687</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -12439,12 +12439,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>108781</t>
+          <t>111944</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>149696</t>
+          <t>150227</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12454,12 +12454,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12474,12 +12474,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>131114</t>
+          <t>130506</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>171846</t>
+          <t>173634</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12509,12 +12509,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>254183</t>
+          <t>250516</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>312705</t>
+          <t>309513</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,29%</t>
         </is>
       </c>
     </row>
@@ -12552,12 +12552,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>164418</t>
+          <t>165898</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>217003</t>
+          <t>216386</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12567,12 +12567,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12587,12 +12587,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>221614</t>
+          <t>224872</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>273590</t>
+          <t>273839</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12622,12 +12622,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>401717</t>
+          <t>403188</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>476097</t>
+          <t>478250</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,44%</t>
         </is>
       </c>
     </row>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>162374</t>
+          <t>165908</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>216003</t>
+          <t>218261</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12680,12 +12680,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12700,12 +12700,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>210580</t>
+          <t>210854</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>268754</t>
+          <t>267771</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12735,12 +12735,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>390372</t>
+          <t>394597</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>472528</t>
+          <t>472332</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,01%</t>
         </is>
       </c>
     </row>
@@ -12778,12 +12778,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>59546</t>
+          <t>59710</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>182741</t>
+          <t>170062</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12793,12 +12793,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12813,12 +12813,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>62414</t>
+          <t>61765</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>91767</t>
+          <t>91154</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -12848,12 +12848,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>133403</t>
+          <t>134088</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>251288</t>
+          <t>269245</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>19,39%</t>
         </is>
       </c>
     </row>
@@ -12891,12 +12891,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>18087</t>
+          <t>18164</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>34006</t>
+          <t>35241</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12906,12 +12906,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -12926,12 +12926,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>20120</t>
+          <t>20335</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>40344</t>
+          <t>41444</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -12941,12 +12941,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -12961,12 +12961,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>42160</t>
+          <t>42998</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>70139</t>
+          <t>69305</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -12976,12 +12976,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
